--- a/laporan_padel_dki_jakarta_2026-10-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-14.xlsx
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.480.000</t>
+          <t>Rp3.670.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.595.000</t>
+          <t>Rp1.894.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp106.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp1.365.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.560.000</t>
+          <t>Rp4.860.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.099.992</t>
+          <t>Rp2.849.992</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-14.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.520.985</t>
+          <t>Rp7.218.983</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp915.000</t>
+          <t>Rp575.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp3.936.000</t>
+          <t>Rp4.146.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp598.000</t>
+          <t>Rp398.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.178.000</t>
+          <t>Rp3.928.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp49.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp19.350.000</t>
+          <t>Rp21.300.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.388.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp470.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp34.150.000</t>
+          <t>Rp34.650.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp168.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.992.000</t>
+          <t>Rp5.391.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.580.000</t>
+          <t>Rp11.780.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp20.326.500</t>
+          <t>Rp20.496.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.885.000</t>
+          <t>Rp16.735.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.116.000</t>
+          <t>Rp5.454.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.525.000</t>
+          <t>Rp10.800.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.633.000</t>
+          <t>Rp7.333.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.520.000</t>
+          <t>Rp4.690.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.925.000</t>
+          <t>Rp12.415.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp9.735.000</t>
+          <t>Rp9.845.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp20.525.000</t>
+          <t>Rp22.325.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.570.000</t>
+          <t>Rp10.870.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.450.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.584.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.310.000</t>
+          <t>Rp22.090.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.615.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.131.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-14.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.702.000</t>
+          <t>Rp1.878.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.218.983</t>
+          <t>Rp6.869.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.154.500</t>
+          <t>Rp9.504.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.530.000</t>
+          <t>Rp3.830.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.850.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp575.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.140.000</t>
+          <t>Rp5.390.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.130.000</t>
+          <t>Rp2.430.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.165.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.582.000</t>
+          <t>Rp5.380.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp4.146.000</t>
+          <t>Rp3.096.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp9.260.000</t>
+          <t>Rp9.700.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.175.000</t>
+          <t>Rp5.612.500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp490.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp3.430.000</t>
+          <t>Rp2.910.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.928.000</t>
+          <t>Rp4.127.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>102</v>
       </c>
       <c r="D85" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp4.170.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.992.000</t>
+          <t>Rp2.290.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.134.000</t>
+          <t>Rp1.296.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp198.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.894.000</t>
+          <t>Rp2.592.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.995.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp32.285.000</t>
+          <t>Rp32.560.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp21.300.000</t>
+          <t>Rp21.150.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.920.000</t>
+          <t>Rp4.452.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.820.000</t>
+          <t>Rp8.520.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.420.000</t>
+          <t>Rp2.070.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.750.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp34.650.000</t>
+          <t>Rp35.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.255.000</t>
+          <t>Rp4.925.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp497.000</t>
+          <t>Rp237.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp11.640.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.975.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp20.496.500</t>
+          <t>Rp20.776.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.390.000</t>
+          <t>Rp2.060.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.190.000</t>
+          <t>Rp4.494.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.735.000</t>
+          <t>Rp17.285.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.800.000</t>
+          <t>Rp9.825.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.333.000</t>
+          <t>Rp7.764.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp265.000</t>
+          <t>Rp465.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.825.000</t>
+          <t>Rp14.925.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.436.000</t>
+          <t>Rp5.724.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.825.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>96</v>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp10.295.000</t>
+          <t>Rp11.222.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.870.000</t>
+          <t>Rp12.250.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp670.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.095.000</t>
+          <t>Rp6.945.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.130.000</t>
+          <t>Rp9.355.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.849.992</t>
+          <t>Rp3.099.992</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.795.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.564.000</t>
+          <t>Rp3.992.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.090.000</t>
+          <t>Rp22.390.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp6.360.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.899.988</t>
+          <t>Rp5.149.988</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.237.000</t>
+          <t>Rp3.882.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.010.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>112</v>
       </c>
       <c r="D36" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.547.000</t>
+          <t>Rp4.746.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp330.000</t>
+          <t>Rp515.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.675.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-14.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.869.984</t>
+          <t>Rp6.831.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.504.500</t>
+          <t>Rp11.154.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.685.000</t>
+          <t>Rp14.380.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp725.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.581.000</t>
+          <t>Rp1.779.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.737.000</t>
+          <t>Rp1.161.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.086.000</t>
+          <t>Rp3.476.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.885.000</t>
+          <t>Rp4.195.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.584.000</t>
+          <t>Rp2.702.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.040.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.390.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.420.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp456.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp446.000</t>
+          <t>Rp1.340.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.277.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.278.000</t>
+          <t>Rp4.631.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.612.500</t>
+          <t>Rp4.737.500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.910.000</t>
+          <t>Rp1.870.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp6.170.000</t>
+          <t>Rp6.570.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp4.655.000</t>
+          <t>Rp4.165.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.127.000</t>
+          <t>Rp4.870.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp2.082.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>102</v>
       </c>
       <c r="D85" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp4.170.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp2.290.000</t>
+          <t>Rp1.294.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp778.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.870.000</t>
+          <t>Rp5.270.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp998.000</t>
+          <t>Rp1.198.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp13.200.000</t>
+          <t>Rp13.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.130.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp485.000</t>
+          <t>Rp1.640.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.978.000</t>
+          <t>Rp7.676.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp32.560.000</t>
+          <t>Rp33.220.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.099.000</t>
+          <t>Rp1.699.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp3.880.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp21.150.000</t>
+          <t>Rp20.250.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp5.899.000</t>
+          <t>Rp4.699.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp470.000</t>
+          <t>Rp1.020.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.520.000</t>
+          <t>Rp8.740.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp10.800.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp580.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.270.000</t>
+          <t>Rp18.150.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.600.000</t>
+          <t>Rp11.300.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.240.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.335.000</t>
+          <t>Rp6.595.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.715.000</t>
+          <t>Rp4.159.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp168.000</t>
+          <t>Rp852.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.391.000</t>
+          <t>Rp4.392.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.780.000</t>
+          <t>Rp12.580.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.640.000</t>
+          <t>Rp12.040.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.975.000</t>
+          <t>Rp6.675.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.513.000</t>
+          <t>Rp7.749.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.060.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.764.000</t>
+          <t>Rp7.239.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.075.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp5.490.000</t>
+          <t>Rp5.710.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp2.245.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.925.000</t>
+          <t>Rp15.125.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>84</v>
       </c>
       <c r="D36" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.825.000</t>
+          <t>Rp6.125.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.152.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.650.000</t>
+          <t>Rp23.350.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp9.845.000</t>
+          <t>Rp10.230.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp22.325.000</t>
+          <t>Rp25.325.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7948,19 +7948,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp11.222.000</t>
+          <t>Rp11.571.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.160.000</t>
+          <t>Rp7.840.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.800.000</t>
+          <t>Rp11.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.388.000</t>
+          <t>Rp3.089.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.460.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.945.000</t>
+          <t>Rp6.435.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.355.000</t>
+          <t>Rp9.085.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.099.992</t>
+          <t>Rp3.874.990</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.120.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.992.000</t>
+          <t>Rp3.342.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp320.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.360.000</t>
+          <t>Rp6.165.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.415.000</t>
+          <t>Rp1.614.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp2.785.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>112</v>
       </c>
       <c r="D36" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.746.000</t>
+          <t>Rp4.547.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.555.000</t>
+          <t>Rp3.455.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-14.xlsx
@@ -544,16 +544,16 @@
         <v>160</v>
       </c>
       <c r="D4" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.320.000</t>
+          <t>Rp13.820.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.830.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.950.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.145.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.710.000</t>
+          <t>Rp2.810.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp749.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.082.000</t>
+          <t>Rp2.379.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.835.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.550.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.150.000</t>
+          <t>Rp19.305.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.300.000</t>
+          <t>Rp11.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp237.000</t>
+          <t>Rp643.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.675.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp20.776.500</t>
+          <t>Rp21.013.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.239.000</t>
+          <t>Rp7.502.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.245.000</t>
+          <t>Rp1.995.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp15.125.000</t>
+          <t>Rp16.275.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp23.350.000</t>
+          <t>Rp23.550.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.874.990</t>
+          <t>Rp3.999.990</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.149.988</t>
+          <t>Rp5.274.988</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.455.000</t>
+          <t>Rp3.755.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-14.xlsx
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.502.000</t>
+          <t>Rp7.512.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.570.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
